--- a/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0003T0006Z000C1N1_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0003T0006Z000C1N1_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>73.89379360895694</v>
+        <v>12.0077414614555</v>
       </c>
       <c r="D2" t="n">
-        <v>75.51526184430817</v>
+        <v>12.27123004970008</v>
       </c>
       <c r="E2" t="n">
-        <v>15.9521198415517</v>
+        <v>2.592219474252151</v>
       </c>
       <c r="F2" t="n">
-        <v>16.66829036730111</v>
+        <v>2.708597184686431</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>44.43612096979697</v>
+        <v>7.220869657592007</v>
       </c>
       <c r="D3" t="n">
-        <v>43.34830933018275</v>
+        <v>7.044100266154698</v>
       </c>
       <c r="E3" t="n">
-        <v>15.9521198415517</v>
+        <v>2.592219474252151</v>
       </c>
       <c r="F3" t="n">
-        <v>16.66829036730111</v>
+        <v>2.708597184686431</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>50.99959582900581</v>
+        <v>8.287434322213445</v>
       </c>
       <c r="D4" t="n">
-        <v>52.41899777815515</v>
+        <v>8.518087138950213</v>
       </c>
       <c r="E4" t="n">
-        <v>15.9521198415517</v>
+        <v>2.592219474252151</v>
       </c>
       <c r="F4" t="n">
-        <v>16.66829036730111</v>
+        <v>2.708597184686431</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>64.52199366095712</v>
+        <v>10.48482396990553</v>
       </c>
       <c r="D5" t="n">
-        <v>66.33517915046835</v>
+        <v>10.77946661195111</v>
       </c>
       <c r="E5" t="n">
-        <v>15.9521198415517</v>
+        <v>2.592219474252151</v>
       </c>
       <c r="F5" t="n">
-        <v>16.66829036730111</v>
+        <v>2.708597184686431</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>56.01532678871548</v>
+        <v>9.102490603166267</v>
       </c>
       <c r="D6" t="n">
-        <v>53.98482603455982</v>
+        <v>8.772534230615971</v>
       </c>
       <c r="E6" t="n">
-        <v>15.9521198415517</v>
+        <v>2.592219474252151</v>
       </c>
       <c r="F6" t="n">
-        <v>16.66829036730111</v>
+        <v>2.708597184686431</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>28.59076599908227</v>
+        <v>4.645999474850869</v>
       </c>
       <c r="D7" t="n">
-        <v>27.3556369497582</v>
+        <v>4.445291004335708</v>
       </c>
       <c r="E7" t="n">
-        <v>15.9521198415517</v>
+        <v>2.592219474252151</v>
       </c>
       <c r="F7" t="n">
-        <v>16.66829036730111</v>
+        <v>2.708597184686431</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>66.71722847879644</v>
+        <v>10.84154962780442</v>
       </c>
       <c r="D8" t="n">
-        <v>64.45832565100073</v>
+        <v>10.47447791828762</v>
       </c>
       <c r="E8" t="n">
-        <v>15.9521198415517</v>
+        <v>2.592219474252151</v>
       </c>
       <c r="F8" t="n">
-        <v>16.66829036730111</v>
+        <v>2.708597184686431</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>30.07685575800867</v>
+        <v>4.887489060676408</v>
       </c>
       <c r="D9" t="n">
-        <v>27.9553959581686</v>
+        <v>4.542751843202398</v>
       </c>
       <c r="E9" t="n">
-        <v>15.9521198415517</v>
+        <v>2.592219474252151</v>
       </c>
       <c r="F9" t="n">
-        <v>16.66829036730111</v>
+        <v>2.708597184686431</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>48.30763293290779</v>
+        <v>7.849990351597516</v>
       </c>
       <c r="D10" t="n">
-        <v>46.03590407902182</v>
+        <v>7.480834412841046</v>
       </c>
       <c r="E10" t="n">
-        <v>15.9521198415517</v>
+        <v>2.592219474252151</v>
       </c>
       <c r="F10" t="n">
-        <v>16.66829036730111</v>
+        <v>2.708597184686431</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>41.39569982900186</v>
+        <v>6.726801222212802</v>
       </c>
       <c r="D11" t="n">
-        <v>39.12159086860987</v>
+        <v>6.357258516149105</v>
       </c>
       <c r="E11" t="n">
-        <v>15.9521198415517</v>
+        <v>2.592219474252151</v>
       </c>
       <c r="F11" t="n">
-        <v>16.66829036730111</v>
+        <v>2.708597184686431</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>4.321541333862347</v>
+        <v>0.7022504667526314</v>
       </c>
       <c r="D12" t="n">
-        <v>2.060788008897763</v>
+        <v>0.3348780514458865</v>
       </c>
       <c r="E12" t="n">
-        <v>15.9521198415517</v>
+        <v>2.592219474252151</v>
       </c>
       <c r="F12" t="n">
-        <v>16.66829036730111</v>
+        <v>2.708597184686431</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>52.03685315454762</v>
+        <v>8.45598863761399</v>
       </c>
       <c r="D13" t="n">
-        <v>54.30988160804318</v>
+        <v>8.825355761307017</v>
       </c>
       <c r="E13" t="n">
-        <v>15.9521198415517</v>
+        <v>2.592219474252151</v>
       </c>
       <c r="F13" t="n">
-        <v>16.66829036730111</v>
+        <v>2.708597184686431</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>35.41107832602923</v>
+        <v>5.75430022797975</v>
       </c>
       <c r="D14" t="n">
-        <v>33.13221907415819</v>
+        <v>5.383985599550705</v>
       </c>
       <c r="E14" t="n">
-        <v>15.9521198415517</v>
+        <v>2.592219474252151</v>
       </c>
       <c r="F14" t="n">
-        <v>16.66829036730111</v>
+        <v>2.708597184686431</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>30.69522287757117</v>
+        <v>4.987973717605315</v>
       </c>
       <c r="D15" t="n">
-        <v>28.48968437993889</v>
+        <v>4.62957371174007</v>
       </c>
       <c r="E15" t="n">
-        <v>15.9521198415517</v>
+        <v>2.592219474252151</v>
       </c>
       <c r="F15" t="n">
-        <v>16.66829036730111</v>
+        <v>2.708597184686431</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>49.77667505302238</v>
+        <v>8.088709696116137</v>
       </c>
       <c r="D16" t="n">
-        <v>47.72546842779515</v>
+        <v>7.755388619516712</v>
       </c>
       <c r="E16" t="n">
-        <v>15.9521198415517</v>
+        <v>2.592219474252151</v>
       </c>
       <c r="F16" t="n">
-        <v>16.66829036730111</v>
+        <v>2.708597184686431</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>42.80277395818054</v>
+        <v>6.955450768204339</v>
       </c>
       <c r="D17" t="n">
-        <v>40.95854479141325</v>
+        <v>6.655763528604654</v>
       </c>
       <c r="E17" t="n">
-        <v>15.9521198415517</v>
+        <v>2.592219474252151</v>
       </c>
       <c r="F17" t="n">
-        <v>16.66829036730111</v>
+        <v>2.708597184686431</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>29.8956261776991</v>
+        <v>4.858039253876104</v>
       </c>
       <c r="D18" t="n">
-        <v>31.27621284708391</v>
+        <v>5.082384587651136</v>
       </c>
       <c r="E18" t="n">
-        <v>15.9521198415517</v>
+        <v>2.592219474252151</v>
       </c>
       <c r="F18" t="n">
-        <v>16.66829036730111</v>
+        <v>2.708597184686431</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>47.48686431740865</v>
+        <v>7.716615451578905</v>
       </c>
       <c r="D19" t="n">
-        <v>48.69262536479538</v>
+        <v>7.91255162177925</v>
       </c>
       <c r="E19" t="n">
-        <v>15.9521198415517</v>
+        <v>2.592219474252151</v>
       </c>
       <c r="F19" t="n">
-        <v>16.66829036730111</v>
+        <v>2.708597184686431</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>57.10821210192419</v>
+        <v>9.28008446656268</v>
       </c>
       <c r="D20" t="n">
-        <v>55.82001301052652</v>
+        <v>9.07075211421056</v>
       </c>
       <c r="E20" t="n">
-        <v>15.9521198415517</v>
+        <v>2.592219474252151</v>
       </c>
       <c r="F20" t="n">
-        <v>16.66829036730111</v>
+        <v>2.708597184686431</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>63.29384192236404</v>
+        <v>10.28524931238416</v>
       </c>
       <c r="D21" t="n">
-        <v>63.14401070948158</v>
+        <v>10.26090174029076</v>
       </c>
       <c r="E21" t="n">
-        <v>15.9521198415517</v>
+        <v>2.592219474252151</v>
       </c>
       <c r="F21" t="n">
-        <v>16.66829036730111</v>
+        <v>2.708597184686431</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
